--- a/SI_SedimentRetentionLiterature.xlsx
+++ b/SI_SedimentRetentionLiterature.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\2026 Delta SedimentRetention\code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\2026 Delta SedimentRetention\GlobalSedimentRetention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD2B676-8C4D-4E1A-8737-C438C19DB0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7A40FD-0AE9-47A9-A06D-1665DA5C392F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -236,16 +236,16 @@
   </cellStyles>
   <dxfs count="22">
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="166" formatCode="0.0E+00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -417,10 +417,10 @@
     </tableColumn>
     <tableColumn id="6" xr3:uid="{B3856A62-F827-473C-9AEB-18C1CFDFCC55}" name="total delta sediment volume (km3)" dataDxfId="7" totalsRowDxfId="6"/>
     <tableColumn id="7" xr3:uid="{34133183-FBD6-4090-95F1-B0A83A15D3AC}" name="fluvial sediment load (m3/yr)" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="21" xr3:uid="{A292E952-A2CA-427B-952D-670332A430EE}" name="fluvial sediment load (kg/s)" dataDxfId="1" totalsRowDxfId="3">
+    <tableColumn id="21" xr3:uid="{A292E952-A2CA-427B-952D-670332A430EE}" name="fluvial sediment load (kg/s)" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[fluvial sediment load (m3/yr)]]/365/3600/24*1600</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E802D308-DBC2-4EBF-8313-7A1A6EFDD24B}" name="retention_literature" dataDxfId="0" totalsRowDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{E802D308-DBC2-4EBF-8313-7A1A6EFDD24B}" name="retention_literature" dataDxfId="1" totalsRowDxfId="0"/>
     <tableColumn id="12" xr3:uid="{4DB951B8-ADC3-4F00-A5D9-8EE2CC9AFC86}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
